--- a/tests/fixtures/expected/gruppen_touren.xlsx
+++ b/tests/fixtures/expected/gruppen_touren.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[dates]2026-08-09 00:00:00 bis 2026-08-09 23:59:59</t>
+          <t>[dates]2026-08-09 00:00:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
